--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M08/run_2/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M08/run_2/CF_M08_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.9355</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.6374</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.9655</v>
       </c>
       <c r="D3" t="n">
+        <v>0.7089</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.965</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5</v>
       </c>
       <c r="D4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8475</v>
       </c>
     </row>
@@ -1226,13 +1240,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_41</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -1251,14 +1263,11 @@
       <c r="P2" t="n">
         <v>78</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M08_P06</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1304,13 +1313,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Observer</t>
@@ -1329,14 +1336,11 @@
       <c r="P3" t="n">
         <v>66</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M08_P04</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1357,7 +1361,6 @@
       <c r="D4" t="n">
         <v>0.8475</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1378,7 +1381,6 @@
           <t>['AU_05', 'AU_06']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_49</t>
@@ -1389,7 +1391,6 @@
           <t>system service (next.js), data service (postgresql)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1408,7 +1409,6 @@
           <t>CF_M08_AU04, CF_M08_AU08</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M08_AU24</t>
@@ -1459,14 +1459,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Security Service</t>
@@ -1490,13 +1487,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1537,14 +1532,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>System Service</t>
@@ -1568,13 +1560,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1615,14 +1605,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Data Service</t>
@@ -1646,13 +1633,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1698,13 +1683,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Singleton</t>
@@ -1723,14 +1706,11 @@
       <c r="P8" t="n">
         <v>67</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M08_P05</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1776,13 +1756,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Cloud storage</t>
@@ -1806,13 +1784,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M08_AU12</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1858,13 +1834,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Payment processing</t>
@@ -1888,13 +1862,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M08_AU14</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1940,13 +1912,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Error monitoring</t>
@@ -1970,13 +1940,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M08_AU18</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2022,13 +1990,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Component-based</t>
@@ -2047,14 +2013,11 @@
       <c r="P12" t="n">
         <v>66</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M08_P03</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2095,14 +2058,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Amazon EC2</t>
@@ -2126,13 +2086,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M08_AU01</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2178,13 +2136,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>React</t>
@@ -2208,13 +2164,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M08_AU06</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2260,13 +2214,11 @@
           <t>['AU_25', 'AU_55']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_26</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Brevo</t>
@@ -2290,13 +2242,11 @@
           <t>CF_M08_AU20</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M08_AU21</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2337,14 +2287,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Docker</t>
@@ -2368,13 +2315,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M08_AU22</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2420,13 +2365,11 @@
           <t>['AU_23', 'AU_54']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Sentry</t>
@@ -2450,13 +2393,11 @@
           <t>CF_M08_AU18</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M08_AU19</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2502,13 +2443,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
@@ -2532,13 +2471,11 @@
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M08_AU08</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2584,13 +2521,11 @@
           <t>['AU_15', 'AU_50']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Google</t>
@@ -2614,13 +2549,11 @@
           <t>CF_M08_AU10</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M08_AU11</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2666,13 +2599,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_25</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Email</t>
@@ -2696,13 +2627,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M08_AU20</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2748,13 +2677,11 @@
           <t>['AU_17', 'AU_51']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2778,13 +2705,11 @@
           <t>CF_M08_AU12</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M08_AU13</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2830,13 +2755,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Authentication</t>
@@ -2860,13 +2783,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M08_AU10</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2912,13 +2833,11 @@
           <t>['AU_19', 'AU_52']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Stripe</t>
@@ -2942,13 +2861,11 @@
           <t>CF_M08_AU14</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M08_AU15</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2994,13 +2911,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Analytics</t>
@@ -3024,13 +2939,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M08_AU16</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3076,13 +2989,11 @@
           <t>['AU_47', 'AU_48']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_46</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>HTTPS</t>
@@ -3101,14 +3012,11 @@
       <c r="P25" t="n">
         <v>43</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M08_AU23</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3149,14 +3057,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -3175,14 +3080,11 @@
       <c r="P26" t="n">
         <v>41</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3228,13 +3130,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Traefik</t>
@@ -3258,13 +3158,11 @@
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3310,13 +3208,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Next.js</t>
@@ -3340,13 +3236,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M08_AU05</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3392,13 +3286,11 @@
           <t>['AU_21', 'AU_53']</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Google Analytics</t>
@@ -3422,13 +3314,11 @@
           <t>CF_M08_AU16</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M08_AU17</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3474,13 +3364,11 @@
           <t>['AU_05', 'AU_49', 'AU_56']</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Prisma</t>
@@ -3504,13 +3392,11 @@
           <t>CF_M08_P02</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M08_AU09</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3584,7 +3470,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Un usuario es todo individuo o entidad que interactúa con el sistema, puede ser tanto un donante como una empresa.</t>
@@ -3620,7 +3505,6 @@
           <t>Empresa</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Una empresa es un tipo de usuario que puede ofrecer productos con sus respectivas rutas para que los donantes los entreguen, comenzando así a crear una cadena.</t>
@@ -3656,7 +3540,6 @@
           <t>Donante</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Un donante es un tipo de usuario que contribuye con productos a una empresa.</t>
@@ -3692,7 +3575,6 @@
           <t>Tailwind CSS</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Next.js soporta varios métodos de estilización, incluyendo módulos CSS, Tailwind CSS y CSS-in-JS, ofreciendo flexibilidad en la gestión de estilos.</t>
@@ -3728,7 +3610,6 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Cabe destacar que para desarrollar el sistema se ha empleado el lenguaje TypeScript.</t>
@@ -3764,7 +3645,6 @@
           <t>Auth.js</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Se ha usado para facilitar la integración con Prisma, más específicamente para manejar la autenticación de usuarios en la aplicación</t>
@@ -3800,7 +3680,6 @@
           <t>Format.js</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Es una librería que sirve para la internacionalización (i18n) de aplicaciones.</t>
@@ -3836,7 +3715,6 @@
           <t>Hook Form</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Este paquete resolvers es una extensión para React Hook Form, una librería para la gestión de formularios en React.</t>
@@ -3872,7 +3750,6 @@
           <t>Radix-ui</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Esta librería incluye una colección de componentes accesibles y estilizados para React</t>
@@ -3908,7 +3785,6 @@
           <t>React email</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Es un conjunto de herramientas para crear y manejar correos electrónicos en aplicaciones React.</t>
@@ -3944,7 +3820,6 @@
           <t>Slugify</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Slugify sirve para convertir cadenas de texto en slugs amigables para la URL.</t>
@@ -3980,7 +3855,6 @@
           <t>Date-fns</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Sirve para manejar fechas en JavaScript.</t>
@@ -4016,7 +3890,6 @@
           <t>Eslint</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Es una librería que se emplea como una herramienta de ’linting’ para JavaScript y TypeScript.</t>
@@ -4052,7 +3925,6 @@
           <t>Negotiator</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Es una librería para la para la ’negociación’ de contenido en HTTP.</t>
@@ -4088,7 +3960,6 @@
           <t>Next-auth</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Es una solución de autenticación para aplicaciones.</t>
@@ -4124,7 +3995,6 @@
           <t>Next-intl</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Es una librería de internacionalización para Next.js.</t>
@@ -4160,7 +4030,6 @@
           <t>Nodemailer</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Es una herramienta que sirve para enviar correos electrónicos desde aplicaciones Node.js.</t>
@@ -4196,7 +4065,6 @@
           <t>Sharp</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Es una librería que sirve para el procesamiento de imágenes.</t>
@@ -4232,7 +4100,6 @@
           <t>Vitest</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Se ha usado como un framework de testing para el proyecto.</t>
@@ -4268,7 +4135,6 @@
           <t>GitLab</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Para desarrollar esta aplicación se ha hecho uso de la herramienta GitLab, la cual facilita el control de versiones</t>
@@ -4304,7 +4170,6 @@
           <t>Terraform</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Terraform es una herramienta de infraestructura como código que permite definir y gestionar la infraestructura de manera declarativa</t>
@@ -4340,7 +4205,6 @@
           <t>HTTP</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Expone los puertos 80 (HTTP) y 443 (HTTPS) al mundo exterior y redirige el tráfico a los servicios internos según las reglas definidas.</t>
@@ -4371,7 +4235,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>security service (traefik), system service (next.js)</t>
@@ -4407,7 +4270,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>system service (next.js), security service (traefik)</t>
@@ -4443,7 +4305,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>system service (next.js), authentication</t>
@@ -4479,7 +4340,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>system service (next.js), cloud storage</t>
@@ -4515,7 +4375,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>system service (next.js), payment processing</t>
@@ -4551,7 +4410,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>system service (next.js), analytics</t>
@@ -4587,7 +4445,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>system service (next.js), error monitoring</t>
@@ -4623,7 +4480,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>system service (next.js), email</t>
@@ -4659,7 +4515,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>data service (postgresql), prisma</t>
@@ -4675,7 +4530,6 @@
           <t>CF_M08_AU24</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>0.7562</v>
       </c>
@@ -4747,7 +4601,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
@@ -4788,7 +4641,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
@@ -4799,7 +4651,6 @@
           <t>AU_49</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0.7163</v>
       </c>
